--- a/課程內容蒐集整理/真靈光進度規劃用.xlsx
+++ b/課程內容蒐集整理/真靈光進度規劃用.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anray\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\true-soul-light-cowork\課程內容蒐集整理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D0B7C9-2851-4DFB-AB04-12070B5E0D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB36D3-86AC-4CEE-8198-8DCEE751047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11730" yWindow="0" windowWidth="25380" windowHeight="16200" xr2:uid="{1C8F3754-27F1-458F-933E-E29B7786EDC8}"/>
+    <workbookView xWindow="18555" yWindow="0" windowWidth="18555" windowHeight="16200" activeTab="1" xr2:uid="{1C8F3754-27F1-458F-933E-E29B7786EDC8}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="企畫書" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>業務部</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,6 +83,109 @@
   </si>
   <si>
     <t>十二月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一季 
+找點找將</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二季 
+海選招募</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三季 
+內部封測</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四季 
+建立系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行銷系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈性系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>運營系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳仲豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立行銷團隊
+捧紅四大 IP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透過流量招募新人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透過流量讓店滿</t>
+  </si>
+  <si>
+    <t>建立行銷系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立靈性課綱
+建立個案示範 100 名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大量海選
+面試練習生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培養練習生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>練習生透過個案練習
+做成培訓系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找點
+徵中醫師、護理師</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝潢
+招募店長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>內部熟客開始進來封測</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做成運營系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徵總經理
+徵特助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立核心決策團隊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行銷系統交棒
+專心講課</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -113,7 +217,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,6 +254,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF793"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -180,7 +296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -204,6 +320,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -211,6 +357,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFF793"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -545,7 +696,7 @@
     <col min="2" max="7" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="7" t="s">
         <v>5</v>
@@ -625,4 +776,100 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D79BF63-7305-4DFF-B149-3E3540F0C700}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
+    <col min="2" max="5" width="26.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14"/>
+      <c r="B1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>